--- a/Sindhi Muslim/Missing Data.xlsx
+++ b/Sindhi Muslim/Missing Data.xlsx
@@ -8,13 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA470285-F0D6-48E4-8A01-8AC88BD1B66E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46DA66AF-E7A8-49DD-860B-5C1EBC98191A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{CB0FC94E-37B2-4FE8-8FB8-1570579AFA9B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{CB0FC94E-37B2-4FE8-8FB8-1570579AFA9B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$1:$H$101</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -34,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="220">
   <si>
     <t>Name</t>
   </si>
@@ -373,13 +377,334 @@
   </si>
   <si>
     <t>S No</t>
+  </si>
+  <si>
+    <t>Azan Fayaz</t>
+  </si>
+  <si>
+    <t>Fayaz Hussain</t>
+  </si>
+  <si>
+    <t>NIC</t>
+  </si>
+  <si>
+    <t>ECE (ROSE)</t>
+  </si>
+  <si>
+    <t>M Fahad</t>
+  </si>
+  <si>
+    <t>Musfirah</t>
+  </si>
+  <si>
+    <t>Faisal</t>
+  </si>
+  <si>
+    <t>Date of Birth</t>
+  </si>
+  <si>
+    <t>Addmission Date</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Ali Usman</t>
+  </si>
+  <si>
+    <t>Rafiq Ali</t>
+  </si>
+  <si>
+    <t>ECE (Daffodil)</t>
+  </si>
+  <si>
+    <t>Areeba</t>
+  </si>
+  <si>
+    <t>Altaf Hussain</t>
+  </si>
+  <si>
+    <t>Class-1</t>
+  </si>
+  <si>
+    <t>Contact</t>
+  </si>
+  <si>
+    <t>Eman</t>
+  </si>
+  <si>
+    <t>Shah Nawaz Khan</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>M. Awais</t>
+  </si>
+  <si>
+    <t>Mehboob Ali</t>
+  </si>
+  <si>
+    <t>M. Raheel</t>
+  </si>
+  <si>
+    <t>Masroor Ali</t>
+  </si>
+  <si>
+    <t>Abdullah</t>
+  </si>
+  <si>
+    <t>Jameel Hussain</t>
+  </si>
+  <si>
+    <t>Abrar</t>
+  </si>
+  <si>
+    <t>Jan Muhammad</t>
+  </si>
+  <si>
+    <t>Mehrunisa</t>
+  </si>
+  <si>
+    <t>Aijaz Ali</t>
+  </si>
+  <si>
+    <t>M. Hassan</t>
+  </si>
+  <si>
+    <t>Manzoor Ahmed</t>
+  </si>
+  <si>
+    <t>M. Mashab</t>
+  </si>
+  <si>
+    <t>Hafizullah</t>
+  </si>
+  <si>
+    <t>Mehboob Ali Lashari</t>
+  </si>
+  <si>
+    <t>Rana Bhutto</t>
+  </si>
+  <si>
+    <t>Azan Ali</t>
+  </si>
+  <si>
+    <t>Akhtiar Hussain</t>
+  </si>
+  <si>
+    <t>Syed Tanzaib Ali</t>
+  </si>
+  <si>
+    <t>Syed Shahid Ali</t>
+  </si>
+  <si>
+    <t>M. Umer</t>
+  </si>
+  <si>
+    <t>Imran Hussain</t>
+  </si>
+  <si>
+    <t>Zain Ali</t>
+  </si>
+  <si>
+    <t>Emaan Noor</t>
+  </si>
+  <si>
+    <t>Noor Mohammad Sahito</t>
+  </si>
+  <si>
+    <t>Mehreen</t>
+  </si>
+  <si>
+    <t>M. Maroof</t>
+  </si>
+  <si>
+    <t>Mahira</t>
+  </si>
+  <si>
+    <t>Arbab Ali Panhwar</t>
+  </si>
+  <si>
+    <t>Meerab</t>
+  </si>
+  <si>
+    <t>Yasir Ahmed</t>
+  </si>
+  <si>
+    <t>Qudsia Zehra</t>
+  </si>
+  <si>
+    <t>Waheed Ali Bhatti</t>
+  </si>
+  <si>
+    <t>Tahamma Fatima</t>
+  </si>
+  <si>
+    <t>Shahzad Ahmed Bhutto</t>
+  </si>
+  <si>
+    <t>Tahamna Batool</t>
+  </si>
+  <si>
+    <t>Zaiba Bakhtawar</t>
+  </si>
+  <si>
+    <t>Abdul Hameed</t>
+  </si>
+  <si>
+    <t>Class-2</t>
+  </si>
+  <si>
+    <t>Ayesha</t>
+  </si>
+  <si>
+    <t>Ali Muhammad</t>
+  </si>
+  <si>
+    <t>Saba Jamali</t>
+  </si>
+  <si>
+    <t>Sajid Ali</t>
+  </si>
+  <si>
+    <t>Taskeen</t>
+  </si>
+  <si>
+    <t>Amjad Ali</t>
+  </si>
+  <si>
+    <t>Afsana</t>
+  </si>
+  <si>
+    <t>Ab. Hafeez</t>
+  </si>
+  <si>
+    <t>Zulfiqar Ali Soomro</t>
+  </si>
+  <si>
+    <t>Abdul Rehman</t>
+  </si>
+  <si>
+    <t>Faizan</t>
+  </si>
+  <si>
+    <t>Lutfullah</t>
+  </si>
+  <si>
+    <t>Fayaz</t>
+  </si>
+  <si>
+    <t>Samano Khan</t>
+  </si>
+  <si>
+    <t>Hammad Ali</t>
+  </si>
+  <si>
+    <t>Sajjad Ali</t>
+  </si>
+  <si>
+    <t>Ahmed Nawaz</t>
+  </si>
+  <si>
+    <t>Ali Nawaz</t>
+  </si>
+  <si>
+    <t>Burair Abbas</t>
+  </si>
+  <si>
+    <t>Azhar Abbas</t>
+  </si>
+  <si>
+    <t>Class-3</t>
+  </si>
+  <si>
+    <t>Munawar Ali</t>
+  </si>
+  <si>
+    <t>Asad Ali</t>
+  </si>
+  <si>
+    <t>Ali Ejaz</t>
+  </si>
+  <si>
+    <t>Arbab Ali</t>
+  </si>
+  <si>
+    <t>Faizan Ahmed</t>
+  </si>
+  <si>
+    <t>Riaz Ahmed</t>
+  </si>
+  <si>
+    <t>M. Shayan</t>
+  </si>
+  <si>
+    <t>Zulfiqar Ali</t>
+  </si>
+  <si>
+    <t>M. Yasin</t>
+  </si>
+  <si>
+    <t>Muneer Ahmed</t>
+  </si>
+  <si>
+    <t>Ghous Bux</t>
+  </si>
+  <si>
+    <t>Shah Fahad</t>
+  </si>
+  <si>
+    <t>M. Ibrahim</t>
+  </si>
+  <si>
+    <t>Shehbaz Ali</t>
+  </si>
+  <si>
+    <t>Zeeshan Hussain</t>
+  </si>
+  <si>
+    <t>M. Hussain</t>
+  </si>
+  <si>
+    <t>Dua Batool</t>
+  </si>
+  <si>
+    <t>Muneer Ahmed Tahiri</t>
+  </si>
+  <si>
+    <t>Fiza</t>
+  </si>
+  <si>
+    <t>Hamid Ali Siyal</t>
+  </si>
+  <si>
+    <t>Hadeeqa</t>
+  </si>
+  <si>
+    <t>Haji Malah</t>
+  </si>
+  <si>
+    <t>Hajul</t>
+  </si>
+  <si>
+    <t>Manzoor Ahmed Memon</t>
+  </si>
+  <si>
+    <t>Insha</t>
+  </si>
+  <si>
+    <t>Fazal Mohammad</t>
+  </si>
+  <si>
+    <t>Mir Amir Udin Mirzada</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -409,16 +734,44 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -561,28 +914,81 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -895,59 +1301,58 @@
   <dimension ref="A1:I32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.28515625" customWidth="1"/>
-    <col min="6" max="6" width="5.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="2"/>
+    <col min="6" max="6" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="11"/>
-      <c r="F1" s="8" t="s">
+      <c r="E1" s="10"/>
+      <c r="F1" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="B2" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="2">
         <v>1</v>
       </c>
       <c r="G2" s="1" t="s">
@@ -956,12 +1361,12 @@
       <c r="H2" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -970,10 +1375,10 @@
       <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="2">
         <v>2</v>
       </c>
       <c r="G3" s="1" t="s">
@@ -982,12 +1387,12 @@
       <c r="H3" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -996,10 +1401,10 @@
       <c r="C4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="2">
         <v>3</v>
       </c>
       <c r="G4" s="1" t="s">
@@ -1008,12 +1413,12 @@
       <c r="H4" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -1022,10 +1427,10 @@
       <c r="C5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="2">
         <v>4</v>
       </c>
       <c r="G5" s="1" t="s">
@@ -1034,24 +1439,24 @@
       <c r="H5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="5">
+      <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="2">
         <v>5</v>
       </c>
       <c r="G6" s="1" t="s">
@@ -1060,16 +1465,12 @@
       <c r="H6" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7"/>
-      <c r="B7"/>
-      <c r="C7"/>
-      <c r="D7"/>
-      <c r="F7" s="3">
+      <c r="F7" s="2">
         <v>6</v>
       </c>
       <c r="G7" s="1" t="s">
@@ -1078,24 +1479,24 @@
       <c r="H7" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="2">
         <v>7</v>
       </c>
       <c r="G8" s="1" t="s">
@@ -1104,12 +1505,12 @@
       <c r="H8" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
+      <c r="A9" s="2">
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -1118,10 +1519,10 @@
       <c r="C9" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="2">
         <v>8</v>
       </c>
       <c r="G9" s="1" t="s">
@@ -1130,12 +1531,12 @@
       <c r="H9" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
+      <c r="A10" s="2">
         <v>2</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -1144,10 +1545,10 @@
       <c r="C10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="2">
         <v>9</v>
       </c>
       <c r="G10" s="1" t="s">
@@ -1156,12 +1557,12 @@
       <c r="H10" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
+      <c r="A11" s="2">
         <v>3</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -1170,10 +1571,10 @@
       <c r="C11" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="2">
         <v>10</v>
       </c>
       <c r="G11" s="1" t="s">
@@ -1182,12 +1583,12 @@
       <c r="H11" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
+      <c r="A12" s="2">
         <v>4</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -1196,10 +1597,10 @@
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="2">
         <v>11</v>
       </c>
       <c r="G12" s="1" t="s">
@@ -1208,12 +1609,12 @@
       <c r="H12" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
+      <c r="A13" s="2">
         <v>5</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -1222,10 +1623,10 @@
       <c r="C13" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="2">
         <v>12</v>
       </c>
       <c r="G13" s="1" t="s">
@@ -1234,12 +1635,12 @@
       <c r="H13" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
+      <c r="A14" s="2">
         <v>6</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -1248,10 +1649,10 @@
       <c r="C14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="2">
         <v>13</v>
       </c>
       <c r="G14" s="1" t="s">
@@ -1260,12 +1661,12 @@
       <c r="H14" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I14" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="3">
+      <c r="A15" s="2">
         <v>7</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -1274,10 +1675,10 @@
       <c r="C15" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="2">
         <v>14</v>
       </c>
       <c r="G15" s="1" t="s">
@@ -1286,12 +1687,12 @@
       <c r="H15" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="I15" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="3">
+      <c r="A16" s="2">
         <v>8</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -1300,10 +1701,10 @@
       <c r="C16" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="2">
         <v>15</v>
       </c>
       <c r="G16" s="1" t="s">
@@ -1312,12 +1713,12 @@
       <c r="H16" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="I16" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
+      <c r="A17" s="2">
         <v>9</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -1326,10 +1727,10 @@
       <c r="C17" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="2">
         <v>16</v>
       </c>
       <c r="G17" s="1" t="s">
@@ -1338,12 +1739,12 @@
       <c r="H17" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="I17" s="4" t="s">
+      <c r="I17" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="3">
+      <c r="A18" s="2">
         <v>10</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -1352,10 +1753,10 @@
       <c r="C18" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="2">
         <v>17</v>
       </c>
       <c r="G18" s="1" t="s">
@@ -1364,12 +1765,12 @@
       <c r="H18" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="I18" s="4" t="s">
+      <c r="I18" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="3">
+      <c r="A19" s="2">
         <v>11</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -1378,10 +1779,10 @@
       <c r="C19" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="2">
         <v>18</v>
       </c>
       <c r="G19" s="1" t="s">
@@ -1390,12 +1791,12 @@
       <c r="H19" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="I19" s="4" t="s">
+      <c r="I19" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="3">
+      <c r="A20" s="2">
         <v>12</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -1404,10 +1805,10 @@
       <c r="C20" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="2">
         <v>19</v>
       </c>
       <c r="G20" s="1" t="s">
@@ -1416,12 +1817,12 @@
       <c r="H20" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="I20" s="4" t="s">
+      <c r="I20" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="3">
+      <c r="A21" s="2">
         <v>13</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -1430,10 +1831,10 @@
       <c r="C21" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="2">
         <v>20</v>
       </c>
       <c r="G21" s="1" t="s">
@@ -1442,12 +1843,12 @@
       <c r="H21" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="I21" s="4" t="s">
+      <c r="I21" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="3">
+      <c r="A22" s="2">
         <v>14</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -1456,10 +1857,10 @@
       <c r="C22" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="2">
         <v>21</v>
       </c>
       <c r="G22" s="1" t="s">
@@ -1468,12 +1869,12 @@
       <c r="H22" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="I22" s="4" t="s">
+      <c r="I22" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="3">
+      <c r="A23" s="2">
         <v>15</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -1482,10 +1883,10 @@
       <c r="C23" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F23" s="3">
+      <c r="F23" s="2">
         <v>22</v>
       </c>
       <c r="G23" s="1" t="s">
@@ -1494,12 +1895,12 @@
       <c r="H23" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="I23" s="4" t="s">
+      <c r="I23" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="3">
+      <c r="A24" s="2">
         <v>16</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -1508,10 +1909,10 @@
       <c r="C24" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F24" s="3">
+      <c r="F24" s="2">
         <v>23</v>
       </c>
       <c r="G24" s="1" t="s">
@@ -1520,12 +1921,12 @@
       <c r="H24" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="I24" s="4" t="s">
+      <c r="I24" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="3">
+      <c r="A25" s="2">
         <v>17</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -1534,10 +1935,10 @@
       <c r="C25" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F25" s="3">
+      <c r="F25" s="2">
         <v>24</v>
       </c>
       <c r="G25" s="1" t="s">
@@ -1546,12 +1947,12 @@
       <c r="H25" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="I25" s="4" t="s">
+      <c r="I25" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="3">
+      <c r="A26" s="2">
         <v>18</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -1560,10 +1961,10 @@
       <c r="C26" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F26" s="3">
+      <c r="F26" s="2">
         <v>25</v>
       </c>
       <c r="G26" s="1" t="s">
@@ -1572,12 +1973,12 @@
       <c r="H26" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="I26" s="4" t="s">
+      <c r="I26" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="3">
+      <c r="A27" s="2">
         <v>19</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -1586,10 +1987,10 @@
       <c r="C27" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F27" s="3">
+      <c r="F27" s="2">
         <v>26</v>
       </c>
       <c r="G27" s="1" t="s">
@@ -1598,24 +1999,24 @@
       <c r="H27" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="I27" s="4" t="s">
+      <c r="I27" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="5">
+      <c r="A28" s="4">
         <v>20</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D28" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F28" s="3">
+      <c r="F28" s="2">
         <v>27</v>
       </c>
       <c r="G28" s="1" t="s">
@@ -1624,12 +2025,12 @@
       <c r="H28" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="I28" s="4" t="s">
+      <c r="I28" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="F29" s="3">
+      <c r="F29" s="2">
         <v>28</v>
       </c>
       <c r="G29" s="1" t="s">
@@ -1638,12 +2039,12 @@
       <c r="H29" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="I29" s="4" t="s">
+      <c r="I29" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="F30" s="3">
+      <c r="F30" s="2">
         <v>29</v>
       </c>
       <c r="G30" s="1" t="s">
@@ -1652,12 +2053,12 @@
       <c r="H30" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="I30" s="4" t="s">
+      <c r="I30" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="F31" s="3">
+      <c r="F31" s="2">
         <v>30</v>
       </c>
       <c r="G31" s="1" t="s">
@@ -1666,21 +2067,21 @@
       <c r="H31" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="I31" s="4" t="s">
+      <c r="I31" s="3" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F32" s="5">
+      <c r="F32" s="4">
         <v>31</v>
       </c>
-      <c r="G32" s="6" t="s">
+      <c r="G32" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="H32" s="6" t="s">
+      <c r="H32" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="I32" s="7" t="s">
+      <c r="I32" s="6" t="s">
         <v>60</v>
       </c>
     </row>
@@ -1688,4 +2089,2660 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16F2B238-2619-40DE-BC1A-55049715D553}">
+  <dimension ref="A1:H101"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="4.5703125" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.42578125" style="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" style="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" style="15" customWidth="1"/>
+    <col min="7" max="7" width="3.7109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7" style="15" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A1" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="F1" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="G1" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="H1" s="17" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="13">
+        <v>1</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="13">
+        <v>2</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="13">
+        <v>3</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="13">
+        <v>4</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="13">
+        <v>5</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="13">
+        <v>6</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H7" s="13" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="13">
+        <v>1</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="13">
+        <v>2</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="13">
+        <v>3</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="13">
+        <v>4</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="13">
+        <v>5</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="13">
+        <v>1</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="13">
+        <v>2</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="13">
+        <v>3</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="13">
+        <v>4</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A17" s="13">
+        <v>5</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="13">
+        <v>6</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="13">
+        <v>7</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A20" s="13">
+        <v>8</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" s="13">
+        <v>9</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G21" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" s="13">
+        <v>10</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A23" s="13">
+        <v>11</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" s="13">
+        <v>12</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" s="13">
+        <v>13</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F25" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" s="13">
+        <v>14</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F26" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H26" s="13" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27" s="13">
+        <v>15</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A28" s="13">
+        <v>16</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G28" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29" s="13">
+        <v>17</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F29" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G29" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H29" s="16" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30" s="13">
+        <v>18</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F30" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G30" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H30" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31" s="13">
+        <v>19</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F31" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G31" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H31" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32" s="13">
+        <v>20</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F32" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G32" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H32" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A33" s="13">
+        <v>21</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="D33" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="E33" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F33" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G33" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H33" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A34" s="13">
+        <v>1</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="E34" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G34" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="H34" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A35" s="13">
+        <v>2</v>
+      </c>
+      <c r="B35" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="D35" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="E35" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F35" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G35" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H35" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A36" s="13">
+        <v>3</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="D36" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="E36" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F36" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G36" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H36" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A37" s="13">
+        <v>4</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="D37" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="E37" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F37" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G37" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H37" s="16" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A38" s="13">
+        <v>5</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C38" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="D38" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="E38" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F38" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G38" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H38" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A39" s="13">
+        <v>6</v>
+      </c>
+      <c r="B39" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="D39" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="E39" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F39" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G39" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H39" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A40" s="13">
+        <v>7</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="C40" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="D40" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="E40" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F40" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G40" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H40" s="16" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A41" s="13">
+        <v>8</v>
+      </c>
+      <c r="B41" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="C41" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="D41" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="E41" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F41" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G41" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H41" s="16" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A42" s="13">
+        <v>9</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C42" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="E42" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="F42" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G42" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="H42" s="16" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A43" s="13">
+        <v>10</v>
+      </c>
+      <c r="B43" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="C43" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="D43" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="E43" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F43" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G43" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H43" s="16" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A44" s="13">
+        <v>11</v>
+      </c>
+      <c r="B44" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="C44" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="D44" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="E44" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F44" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G44" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H44" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A45" s="13">
+        <v>12</v>
+      </c>
+      <c r="B45" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C45" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D45" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="E45" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F45" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G45" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="H45" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A46" s="13">
+        <v>13</v>
+      </c>
+      <c r="B46" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="C46" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="D46" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="E46" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F46" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G46" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H46" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A47" s="13">
+        <v>14</v>
+      </c>
+      <c r="B47" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="C47" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="D47" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="E47" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F47" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G47" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H47" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A48" s="13">
+        <v>15</v>
+      </c>
+      <c r="B48" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C48" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D48" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="E48" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F48" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G48" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H48" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A49" s="13">
+        <v>16</v>
+      </c>
+      <c r="B49" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="C49" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="D49" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="E49" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F49" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G49" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H49" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A50" s="13">
+        <v>17</v>
+      </c>
+      <c r="B50" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C50" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D50" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="E50" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F50" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G50" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H50" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A51" s="13">
+        <v>18</v>
+      </c>
+      <c r="B51" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C51" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D51" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="E51" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F51" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G51" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H51" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A52" s="13">
+        <v>19</v>
+      </c>
+      <c r="B52" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="C52" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="D52" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="E52" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F52" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G52" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H52" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A53" s="13">
+        <v>20</v>
+      </c>
+      <c r="B53" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C53" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D53" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="E53" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F53" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G53" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="H53" s="16" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A54" s="13">
+        <v>21</v>
+      </c>
+      <c r="B54" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C54" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D54" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="E54" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F54" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G54" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H54" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A55" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="B55" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C55" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="D55" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E55" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="F55" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="G55" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="H55" s="17" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A56" s="13">
+        <v>22</v>
+      </c>
+      <c r="B56" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C56" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="D56" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="E56" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F56" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G56" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H56" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A57" s="13">
+        <v>23</v>
+      </c>
+      <c r="B57" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C57" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D57" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="E57" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F57" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G57" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H57" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A58" s="13">
+        <v>24</v>
+      </c>
+      <c r="B58" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C58" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D58" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="E58" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F58" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G58" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H58" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A59" s="13">
+        <v>25</v>
+      </c>
+      <c r="B59" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="C59" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="D59" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="E59" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F59" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G59" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H59" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A60" s="13">
+        <v>1</v>
+      </c>
+      <c r="B60" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C60" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D60" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E60" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="F60" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G60" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="H60" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A61" s="13">
+        <v>2</v>
+      </c>
+      <c r="B61" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C61" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D61" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E61" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F61" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G61" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="H61" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A62" s="13">
+        <v>3</v>
+      </c>
+      <c r="B62" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="C62" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="D62" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E62" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F62" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G62" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H62" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A63" s="13">
+        <v>4</v>
+      </c>
+      <c r="B63" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="C63" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="D63" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E63" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F63" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G63" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H63" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A64" s="13">
+        <v>5</v>
+      </c>
+      <c r="B64" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C64" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="D64" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E64" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F64" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G64" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H64" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A65" s="13">
+        <v>6</v>
+      </c>
+      <c r="B65" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="C65" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D65" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E65" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F65" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G65" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H65" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A66" s="13">
+        <v>7</v>
+      </c>
+      <c r="B66" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="C66" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="D66" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E66" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F66" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G66" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H66" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A67" s="13">
+        <v>8</v>
+      </c>
+      <c r="B67" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C67" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="D67" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E67" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F67" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G67" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H67" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A68" s="13">
+        <v>9</v>
+      </c>
+      <c r="B68" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="C68" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="D68" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E68" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F68" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G68" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H68" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A69" s="13">
+        <v>10</v>
+      </c>
+      <c r="B69" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C69" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D69" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E69" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="F69" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G69" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="H69" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A70" s="13">
+        <v>11</v>
+      </c>
+      <c r="B70" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="C70" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="D70" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E70" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F70" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G70" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H70" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A71" s="13">
+        <v>12</v>
+      </c>
+      <c r="B71" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C71" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="D71" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E71" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F71" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G71" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H71" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A72" s="13">
+        <v>13</v>
+      </c>
+      <c r="B72" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="C72" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="D72" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E72" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F72" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G72" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H72" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A73" s="13">
+        <v>14</v>
+      </c>
+      <c r="B73" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="C73" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="D73" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E73" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F73" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G73" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H73" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A74" s="13">
+        <v>15</v>
+      </c>
+      <c r="B74" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="C74" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D74" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E74" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F74" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G74" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H74" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A75" s="13">
+        <v>16</v>
+      </c>
+      <c r="B75" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="C75" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D75" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E75" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F75" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G75" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H75" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A76" s="13">
+        <v>17</v>
+      </c>
+      <c r="B76" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C76" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="D76" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E76" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F76" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G76" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H76" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A77" s="13">
+        <v>18</v>
+      </c>
+      <c r="B77" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C77" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="D77" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E77" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F77" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G77" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H77" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A78" s="13">
+        <v>19</v>
+      </c>
+      <c r="B78" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="C78" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="D78" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E78" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F78" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G78" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H78" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A79" s="13">
+        <v>20</v>
+      </c>
+      <c r="B79" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="C79" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="D79" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E79" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F79" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G79" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H79" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A80" s="13">
+        <v>21</v>
+      </c>
+      <c r="B80" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C80" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="D80" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E80" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F80" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G80" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H80" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A81" s="13">
+        <v>22</v>
+      </c>
+      <c r="B81" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="C81" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="D81" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E81" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="F81" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G81" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="H81" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A82" s="13">
+        <v>23</v>
+      </c>
+      <c r="B82" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C82" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="D82" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E82" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F82" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G82" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H82" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A83" s="13">
+        <v>24</v>
+      </c>
+      <c r="B83" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="C83" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="D83" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E83" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F83" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G83" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H83" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A84" s="13">
+        <v>25</v>
+      </c>
+      <c r="B84" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="C84" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="D84" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E84" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F84" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G84" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H84" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A85" s="13">
+        <v>26</v>
+      </c>
+      <c r="B85" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="C85" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="D85" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E85" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F85" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G85" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H85" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A86" s="13">
+        <v>27</v>
+      </c>
+      <c r="B86" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="C86" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="D86" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E86" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F86" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G86" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H86" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A87" s="13">
+        <v>28</v>
+      </c>
+      <c r="B87" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="C87" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="D87" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E87" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F87" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="G87" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H87" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A88" s="13">
+        <v>29</v>
+      </c>
+      <c r="B88" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="C88" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="D88" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E88" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="F88" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G88" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="H88" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A89" s="13">
+        <v>30</v>
+      </c>
+      <c r="B89" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="C89" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="D89" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E89" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="F89" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G89" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H89" s="16" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A90" s="13">
+        <v>31</v>
+      </c>
+      <c r="B90" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="C90" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="D90" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E90" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="F90" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G90" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H90" s="16" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A91" s="13">
+        <v>32</v>
+      </c>
+      <c r="B91" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="C91" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="D91" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E91" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="F91" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G91" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="H91" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A92" s="13">
+        <v>33</v>
+      </c>
+      <c r="B92" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C92" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D92" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E92" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="F92" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G92" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H92" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A93" s="13">
+        <v>34</v>
+      </c>
+      <c r="B93" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="C93" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="D93" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E93" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="F93" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G93" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="H93" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A94" s="13">
+        <v>35</v>
+      </c>
+      <c r="B94" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="C94" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="D94" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E94" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="F94" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G94" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="H94" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A95" s="13">
+        <v>36</v>
+      </c>
+      <c r="B95" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="C95" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="D95" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E95" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="F95" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G95" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H95" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A96" s="13">
+        <v>37</v>
+      </c>
+      <c r="B96" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="C96" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="D96" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E96" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="F96" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G96" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H96" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A97" s="13">
+        <v>38</v>
+      </c>
+      <c r="B97" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="C97" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D97" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E97" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="F97" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G97" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H97" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A98" s="13">
+        <v>39</v>
+      </c>
+      <c r="B98" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="C98" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="D98" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E98" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="F98" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G98" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="H98" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A99" s="13">
+        <v>40</v>
+      </c>
+      <c r="B99" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="C99" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="D99" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E99" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="F99" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G99" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="H99" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A100" s="13">
+        <v>41</v>
+      </c>
+      <c r="B100" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="C100" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="D100" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E100" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="F100" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G100" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="H100" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A101" s="13">
+        <v>42</v>
+      </c>
+      <c r="B101" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="C101" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="D101" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="E101" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="F101" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G101" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="H101" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="E1:H1048576">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>"yes"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+      <formula>"no"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Sindhi Muslim/Missing Data.xlsx
+++ b/Sindhi Muslim/Missing Data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Government-High-School\Sindhi Muslim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46DA66AF-E7A8-49DD-860B-5C1EBC98191A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{479B808D-E83D-4F2E-AA2F-6466F34B5C7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{CB0FC94E-37B2-4FE8-8FB8-1570579AFA9B}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$1:$H$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$1:$H$55</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="180">
   <si>
     <t>Name</t>
   </si>
@@ -481,12 +481,6 @@
     <t>Hafizullah</t>
   </si>
   <si>
-    <t>Mehboob Ali Lashari</t>
-  </si>
-  <si>
-    <t>Rana Bhutto</t>
-  </si>
-  <si>
     <t>Azan Ali</t>
   </si>
   <si>
@@ -499,12 +493,6 @@
     <t>Syed Shahid Ali</t>
   </si>
   <si>
-    <t>M. Umer</t>
-  </si>
-  <si>
-    <t>Imran Hussain</t>
-  </si>
-  <si>
     <t>Zain Ali</t>
   </si>
   <si>
@@ -559,21 +547,6 @@
     <t>Ayesha</t>
   </si>
   <si>
-    <t>Ali Muhammad</t>
-  </si>
-  <si>
-    <t>Saba Jamali</t>
-  </si>
-  <si>
-    <t>Sajid Ali</t>
-  </si>
-  <si>
-    <t>Taskeen</t>
-  </si>
-  <si>
-    <t>Amjad Ali</t>
-  </si>
-  <si>
     <t>Afsana</t>
   </si>
   <si>
@@ -583,33 +556,12 @@
     <t>Zulfiqar Ali Soomro</t>
   </si>
   <si>
-    <t>Abdul Rehman</t>
-  </si>
-  <si>
-    <t>Faizan</t>
-  </si>
-  <si>
-    <t>Lutfullah</t>
-  </si>
-  <si>
-    <t>Fayaz</t>
-  </si>
-  <si>
-    <t>Samano Khan</t>
-  </si>
-  <si>
     <t>Hammad Ali</t>
   </si>
   <si>
     <t>Sajjad Ali</t>
   </si>
   <si>
-    <t>Ahmed Nawaz</t>
-  </si>
-  <si>
-    <t>Ali Nawaz</t>
-  </si>
-  <si>
     <t>Burair Abbas</t>
   </si>
   <si>
@@ -619,85 +571,13 @@
     <t>Class-3</t>
   </si>
   <si>
-    <t>Munawar Ali</t>
-  </si>
-  <si>
-    <t>Asad Ali</t>
-  </si>
-  <si>
-    <t>Ali Ejaz</t>
-  </si>
-  <si>
-    <t>Arbab Ali</t>
-  </si>
-  <si>
-    <t>Faizan Ahmed</t>
-  </si>
-  <si>
-    <t>Riaz Ahmed</t>
-  </si>
-  <si>
-    <t>M. Shayan</t>
-  </si>
-  <si>
-    <t>Zulfiqar Ali</t>
-  </si>
-  <si>
     <t>M. Yasin</t>
   </si>
   <si>
-    <t>Muneer Ahmed</t>
-  </si>
-  <si>
-    <t>Ghous Bux</t>
-  </si>
-  <si>
-    <t>Shah Fahad</t>
-  </si>
-  <si>
-    <t>M. Ibrahim</t>
-  </si>
-  <si>
-    <t>Shehbaz Ali</t>
-  </si>
-  <si>
-    <t>Zeeshan Hussain</t>
-  </si>
-  <si>
-    <t>M. Hussain</t>
-  </si>
-  <si>
-    <t>Dua Batool</t>
-  </si>
-  <si>
-    <t>Muneer Ahmed Tahiri</t>
-  </si>
-  <si>
-    <t>Fiza</t>
-  </si>
-  <si>
-    <t>Hamid Ali Siyal</t>
-  </si>
-  <si>
-    <t>Hadeeqa</t>
-  </si>
-  <si>
-    <t>Haji Malah</t>
-  </si>
-  <si>
-    <t>Hajul</t>
-  </si>
-  <si>
-    <t>Manzoor Ahmed Memon</t>
-  </si>
-  <si>
-    <t>Insha</t>
-  </si>
-  <si>
-    <t>Fazal Mohammad</t>
-  </si>
-  <si>
-    <t>Mir Amir Udin Mirzada</t>
+    <t>Ali Sher</t>
+  </si>
+  <si>
+    <t>Rajab Ali</t>
   </si>
 </sst>
 </file>
@@ -735,14 +615,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -752,6 +624,14 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -942,7 +822,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
@@ -956,11 +836,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2093,7 +1972,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16F2B238-2619-40DE-BC1A-55049715D553}">
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:H102"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="15" bestFit="1" customWidth="1"/>
@@ -2107,29 +1986,29 @@
     <col min="9" max="16384" width="9.140625" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="H1" s="16" t="s">
         <v>129</v>
       </c>
     </row>
@@ -2291,16 +2170,16 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="13">
-        <v>1</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>140</v>
+        <v>7</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>179</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="E8" s="13" t="s">
         <v>122</v>
@@ -2317,13 +2196,13 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="D9" s="13" t="s">
         <v>125</v>
@@ -2332,33 +2211,33 @@
         <v>122</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="G9" s="13" t="s">
         <v>122</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>3</v>
+        <v>114</v>
       </c>
       <c r="D10" s="13" t="s">
         <v>125</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="G10" s="13" t="s">
         <v>122</v>
@@ -2369,22 +2248,22 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>127</v>
+        <v>3</v>
       </c>
       <c r="D11" s="13" t="s">
         <v>125</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="G11" s="13" t="s">
         <v>122</v>
@@ -2395,13 +2274,13 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B12" s="14" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="D12" s="13" t="s">
         <v>125</v>
@@ -2410,62 +2289,62 @@
         <v>122</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="G12" s="13" t="s">
         <v>122</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="13">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>5</v>
+        <v>141</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>128</v>
+        <v>142</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>125</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="G13" s="13" t="s">
         <v>122</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="13" t="s">
         <v>128</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="H14" s="13" t="s">
         <v>122</v>
@@ -2473,51 +2352,51 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="13" t="s">
         <v>128</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>132</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>143</v>
+        <v>10</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="D16" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" s="13" t="s">
         <v>128</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="H16" s="13" t="s">
         <v>132</v>
@@ -2525,15 +2404,15 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>12</v>
+        <v>143</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="D17" s="13" t="s">
         <v>128</v>
       </c>
       <c r="E17" s="13" t="s">
@@ -2543,23 +2422,23 @@
         <v>122</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>145</v>
+        <v>12</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="D18" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="13" t="s">
         <v>128</v>
       </c>
       <c r="E18" s="13" t="s">
@@ -2569,93 +2448,93 @@
         <v>122</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>14</v>
+        <v>145</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D19" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="D19" s="13" t="s">
         <v>128</v>
       </c>
       <c r="E19" s="13" t="s">
         <v>122</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="D20" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="13" t="s">
         <v>128</v>
       </c>
       <c r="E20" s="13" t="s">
         <v>122</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>46</v>
+        <v>147</v>
       </c>
       <c r="C21" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="D21" s="16" t="s">
+      <c r="D21" s="13" t="s">
         <v>128</v>
       </c>
       <c r="E21" s="13" t="s">
         <v>122</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="G21" s="13" t="s">
         <v>122</v>
       </c>
       <c r="H21" s="13" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B22" s="14" t="s">
         <v>149</v>
@@ -2663,33 +2542,33 @@
       <c r="C22" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="D22" s="16" t="s">
+      <c r="D22" s="13" t="s">
         <v>128</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>122</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>122</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="13">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B23" s="14" t="s">
         <v>151</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="D23" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="D23" s="13" t="s">
         <v>128</v>
       </c>
       <c r="E23" s="13" t="s">
@@ -2707,15 +2586,15 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="13">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="C24" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="C24" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="D24" s="16" t="s">
+      <c r="D24" s="13" t="s">
         <v>128</v>
       </c>
       <c r="E24" s="13" t="s">
@@ -2733,15 +2612,15 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="13">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B25" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="C25" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="C25" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="D25" s="16" t="s">
+      <c r="D25" s="13" t="s">
         <v>128</v>
       </c>
       <c r="E25" s="13" t="s">
@@ -2759,7 +2638,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="13">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B26" s="14" t="s">
         <v>156</v>
@@ -2767,7 +2646,7 @@
       <c r="C26" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="D26" s="16" t="s">
+      <c r="D26" s="13" t="s">
         <v>128</v>
       </c>
       <c r="E26" s="13" t="s">
@@ -2785,7 +2664,7 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="13">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B27" s="14" t="s">
         <v>158</v>
@@ -2793,25 +2672,25 @@
       <c r="C27" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="D27" s="16" t="s">
+      <c r="D27" s="13" t="s">
         <v>128</v>
       </c>
       <c r="E27" s="13" t="s">
         <v>122</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>122</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="13">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B28" s="14" t="s">
         <v>160</v>
@@ -2819,14 +2698,14 @@
       <c r="C28" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="D28" s="16" t="s">
+      <c r="D28" s="13" t="s">
         <v>128</v>
       </c>
       <c r="E28" s="13" t="s">
         <v>122</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="G28" s="13" t="s">
         <v>122</v>
@@ -2837,7 +2716,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="13">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B29" s="14" t="s">
         <v>162</v>
@@ -2845,103 +2724,103 @@
       <c r="C29" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="D29" s="16" t="s">
+      <c r="D29" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="E29" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F29" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="G29" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H29" s="16" t="s">
-        <v>122</v>
+      <c r="E29" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="13">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B30" s="14" t="s">
         <v>164</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="D30" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="D30" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="E30" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F30" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="G30" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H30" s="16" t="s">
+      <c r="E30" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H30" s="13" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="13">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B31" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="C31" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="C31" s="14" t="s">
-        <v>167</v>
-      </c>
-      <c r="D31" s="16" t="s">
+      <c r="D31" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="E31" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F31" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G31" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H31" s="16" t="s">
+      <c r="E31" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H31" s="13" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="13">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>168</v>
+        <v>18</v>
       </c>
       <c r="C32" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="D32" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="E32" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F32" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G32" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H32" s="16" t="s">
+      <c r="E32" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F32" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G32" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="H32" s="13" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="13">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="B33" s="14" t="s">
         <v>169</v>
@@ -2949,1790 +2828,632 @@
       <c r="C33" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="D33" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="E33" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F33" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G33" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H33" s="16" t="s">
-        <v>132</v>
+      <c r="D33" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F33" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="G33" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>18</v>
+        <v>168</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D34" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="E34" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F34" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G34" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="H34" s="16" t="s">
-        <v>132</v>
+        <v>170</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="E34" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F34" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="G34" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H34" s="13" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>172</v>
+        <v>25</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="D35" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="E35" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F35" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G35" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H35" s="16" t="s">
-        <v>132</v>
+        <v>26</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="F35" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="G35" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="H35" s="13" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>21</v>
+        <v>168</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="D36" s="16" t="s">
         <v>171</v>
       </c>
-      <c r="E36" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F36" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G36" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H36" s="16" t="s">
-        <v>132</v>
+      <c r="D36" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="E36" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F36" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="G36" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H36" s="13" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="13">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="D37" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="E37" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F37" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="G37" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H37" s="16" t="s">
-        <v>122</v>
+        <v>173</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="E37" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F37" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G37" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H37" s="13" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="D38" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="E38" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F38" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G38" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H38" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="E38" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F38" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G38" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H38" s="13" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B39" s="14" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="D39" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="E39" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F39" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G39" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H39" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="E39" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F39" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="G39" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H39" s="13" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="13">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>178</v>
+        <v>53</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="D40" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="E40" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F40" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="G40" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H40" s="16" t="s">
-        <v>122</v>
+        <v>54</v>
+      </c>
+      <c r="D40" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="E40" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="F40" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="G40" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="H40" s="13" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="13">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B41" s="14" t="s">
-        <v>172</v>
+        <v>63</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="D41" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="E41" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F41" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="G41" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H41" s="16" t="s">
-        <v>122</v>
+        <v>64</v>
+      </c>
+      <c r="D41" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="E41" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F41" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G41" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H41" s="13" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="13">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B42" s="14" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="D42" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="E42" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="F42" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="G42" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="H42" s="16" t="s">
-        <v>122</v>
+        <v>66</v>
+      </c>
+      <c r="D42" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="E42" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F42" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G42" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H42" s="13" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="13">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="D43" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="E43" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F43" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="G43" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H43" s="16" t="s">
-        <v>122</v>
+        <v>131</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="E43" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F43" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="G43" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H43" s="13" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="13">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>181</v>
+        <v>76</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="D44" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="E44" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F44" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G44" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H44" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D44" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="E44" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F44" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="G44" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H44" s="13" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="13">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B45" s="14" t="s">
-        <v>27</v>
+        <v>78</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="D45" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="E45" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F45" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G45" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="H45" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="D45" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="E45" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F45" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="G45" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H45" s="13" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="13">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B46" s="14" t="s">
-        <v>182</v>
+        <v>79</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>183</v>
-      </c>
-      <c r="D46" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="E46" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F46" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G46" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H46" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="D46" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="E46" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="F46" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="G46" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="H46" s="13" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="13">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B47" s="14" t="s">
-        <v>184</v>
+        <v>83</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="D47" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="E47" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F47" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G47" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H47" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D47" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="E47" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="F47" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="G47" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="H47" s="13" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="13">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>29</v>
+        <v>93</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D48" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="E48" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F48" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G48" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H48" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D48" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="E48" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F48" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="G48" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H48" s="13" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="13">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>186</v>
+        <v>95</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="D49" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="E49" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F49" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G49" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H49" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D49" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="E49" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="F49" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="G49" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="H49" s="13" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="13">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B50" s="14" t="s">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D50" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="E50" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F50" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G50" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H50" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="D50" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="E50" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="F50" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="G50" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="H50" s="13" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="13">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B51" s="14" t="s">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="D51" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="E51" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F51" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G51" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H51" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="D51" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="E51" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="F51" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="G51" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="H51" s="13" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="13">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B52" s="14" t="s">
-        <v>188</v>
+        <v>104</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="D52" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="E52" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F52" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G52" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H52" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="D52" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="E52" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="F52" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="G52" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="H52" s="13" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="13">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B53" s="14" t="s">
-        <v>40</v>
+        <v>106</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="D53" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="E53" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F53" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G53" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="H53" s="16" t="s">
-        <v>122</v>
+        <v>107</v>
+      </c>
+      <c r="D53" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="E53" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="F53" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="G53" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="H53" s="13" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="13">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B54" s="14" t="s">
-        <v>44</v>
+        <v>108</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="D54" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="E54" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F54" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G54" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H54" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A55" s="17" t="s">
-        <v>112</v>
-      </c>
-      <c r="B55" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="C55" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="D55" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="E55" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="F55" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="G55" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="H55" s="17" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A56" s="13">
-        <v>22</v>
-      </c>
-      <c r="B56" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="C56" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="D56" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="E56" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F56" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G56" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H56" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A57" s="13">
-        <v>23</v>
-      </c>
-      <c r="B57" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="C57" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="D57" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="E57" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F57" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G57" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H57" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A58" s="13">
-        <v>24</v>
-      </c>
-      <c r="B58" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="C58" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D58" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="E58" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F58" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G58" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H58" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A59" s="13">
-        <v>25</v>
-      </c>
-      <c r="B59" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="C59" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="D59" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="E59" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F59" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="G59" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H59" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A60" s="13">
-        <v>1</v>
-      </c>
-      <c r="B60" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="C60" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="D60" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E60" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="F60" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="G60" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="H60" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A61" s="13">
-        <v>2</v>
-      </c>
-      <c r="B61" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="C61" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="D61" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E61" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F61" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G61" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="H61" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A62" s="13">
-        <v>3</v>
-      </c>
-      <c r="B62" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="C62" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="D62" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E62" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F62" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G62" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H62" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A63" s="13">
-        <v>4</v>
-      </c>
-      <c r="B63" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="C63" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="D63" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E63" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F63" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G63" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H63" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A64" s="13">
-        <v>5</v>
-      </c>
-      <c r="B64" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="C64" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="D64" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E64" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F64" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G64" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H64" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A65" s="13">
-        <v>6</v>
-      </c>
-      <c r="B65" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="C65" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="D65" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E65" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F65" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G65" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H65" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A66" s="13">
-        <v>7</v>
-      </c>
-      <c r="B66" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="C66" s="14" t="s">
-        <v>198</v>
-      </c>
-      <c r="D66" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E66" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F66" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G66" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H66" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A67" s="13">
-        <v>8</v>
-      </c>
-      <c r="B67" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="C67" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="D67" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E67" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F67" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G67" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H67" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A68" s="13">
-        <v>9</v>
-      </c>
-      <c r="B68" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="C68" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="D68" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E68" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F68" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G68" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H68" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A69" s="13">
-        <v>10</v>
-      </c>
-      <c r="B69" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="C69" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D69" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E69" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="F69" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="G69" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="H69" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A70" s="13">
-        <v>11</v>
-      </c>
-      <c r="B70" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="C70" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="D70" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E70" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F70" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G70" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H70" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A71" s="13">
-        <v>12</v>
-      </c>
-      <c r="B71" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C71" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="D71" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E71" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F71" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="G71" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H71" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A72" s="13">
-        <v>13</v>
-      </c>
-      <c r="B72" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="C72" s="14" t="s">
-        <v>203</v>
-      </c>
-      <c r="D72" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E72" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F72" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G72" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H72" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A73" s="13">
-        <v>14</v>
-      </c>
-      <c r="B73" s="14" t="s">
-        <v>204</v>
-      </c>
-      <c r="C73" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="D73" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E73" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F73" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G73" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H73" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A74" s="13">
-        <v>15</v>
-      </c>
-      <c r="B74" s="14" t="s">
-        <v>206</v>
-      </c>
-      <c r="C74" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D74" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E74" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F74" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G74" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H74" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A75" s="13">
+        <v>109</v>
+      </c>
+      <c r="D54" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="E54" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="F54" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="G54" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="H54" s="13" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A55" s="13">
         <v>16</v>
       </c>
-      <c r="B75" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="C75" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D75" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E75" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F75" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G75" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H75" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A76" s="13">
-        <v>17</v>
-      </c>
-      <c r="B76" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="C76" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="D76" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E76" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F76" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G76" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H76" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A77" s="13">
-        <v>18</v>
-      </c>
-      <c r="B77" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="C77" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="D77" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E77" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F77" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G77" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H77" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A78" s="13">
-        <v>19</v>
-      </c>
-      <c r="B78" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="C78" s="14" t="s">
-        <v>208</v>
-      </c>
-      <c r="D78" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E78" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F78" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G78" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H78" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A79" s="13">
-        <v>20</v>
-      </c>
-      <c r="B79" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="C79" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="D79" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E79" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F79" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="G79" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H79" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A80" s="13">
-        <v>21</v>
-      </c>
-      <c r="B80" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="C80" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="D80" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E80" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F80" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="G80" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H80" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A81" s="13">
-        <v>22</v>
-      </c>
-      <c r="B81" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="C81" s="14" t="s">
-        <v>80</v>
-      </c>
-      <c r="D81" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E81" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="F81" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="G81" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="H81" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A82" s="13">
-        <v>23</v>
-      </c>
-      <c r="B82" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="C82" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="D82" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E82" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F82" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G82" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H82" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A83" s="13">
-        <v>24</v>
-      </c>
-      <c r="B83" s="14" t="s">
-        <v>209</v>
-      </c>
-      <c r="C83" s="14" t="s">
-        <v>210</v>
-      </c>
-      <c r="D83" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E83" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F83" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G83" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H83" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A84" s="13">
-        <v>25</v>
-      </c>
-      <c r="B84" s="14" t="s">
-        <v>211</v>
-      </c>
-      <c r="C84" s="14" t="s">
-        <v>212</v>
-      </c>
-      <c r="D84" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E84" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F84" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G84" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H84" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A85" s="13">
-        <v>26</v>
-      </c>
-      <c r="B85" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="C85" s="14" t="s">
-        <v>214</v>
-      </c>
-      <c r="D85" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E85" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F85" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G85" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H85" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A86" s="13">
-        <v>27</v>
-      </c>
-      <c r="B86" s="14" t="s">
-        <v>215</v>
-      </c>
-      <c r="C86" s="14" t="s">
-        <v>216</v>
-      </c>
-      <c r="D86" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E86" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F86" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G86" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H86" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A87" s="13">
-        <v>28</v>
-      </c>
-      <c r="B87" s="14" t="s">
-        <v>217</v>
-      </c>
-      <c r="C87" s="14" t="s">
-        <v>218</v>
-      </c>
-      <c r="D87" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E87" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F87" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="G87" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H87" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A88" s="13">
-        <v>29</v>
-      </c>
-      <c r="B88" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="C88" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="D88" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E88" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="F88" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="G88" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="H88" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A89" s="13">
-        <v>30</v>
-      </c>
-      <c r="B89" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="C89" s="14" t="s">
-        <v>219</v>
-      </c>
-      <c r="D89" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E89" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="F89" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="G89" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H89" s="16" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A90" s="13">
-        <v>31</v>
-      </c>
-      <c r="B90" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="C90" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="D90" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E90" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="F90" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="G90" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H90" s="16" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A91" s="13">
-        <v>32</v>
-      </c>
-      <c r="B91" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="C91" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="D91" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E91" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="F91" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="G91" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="H91" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A92" s="13">
-        <v>33</v>
-      </c>
-      <c r="B92" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="C92" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="D92" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E92" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="F92" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="G92" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H92" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A93" s="13">
-        <v>34</v>
-      </c>
-      <c r="B93" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="C93" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="D93" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E93" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="F93" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="G93" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="H93" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A94" s="13">
-        <v>35</v>
-      </c>
-      <c r="B94" s="14" t="s">
-        <v>97</v>
-      </c>
-      <c r="C94" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="D94" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E94" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="F94" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="G94" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="H94" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A95" s="13">
-        <v>36</v>
-      </c>
-      <c r="B95" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="C95" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="D95" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E95" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="F95" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="G95" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H95" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A96" s="13">
-        <v>37</v>
-      </c>
-      <c r="B96" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="C96" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="D96" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E96" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="F96" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="G96" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H96" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A97" s="13">
-        <v>38</v>
-      </c>
-      <c r="B97" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="C97" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D97" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E97" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="F97" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="G97" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="H97" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A98" s="13">
-        <v>39</v>
-      </c>
-      <c r="B98" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="C98" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="D98" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E98" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="F98" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="G98" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="H98" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A99" s="13">
-        <v>40</v>
-      </c>
-      <c r="B99" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="C99" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="D99" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E99" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="F99" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="G99" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="H99" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A100" s="13">
-        <v>41</v>
-      </c>
-      <c r="B100" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="C100" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="D100" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E100" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="F100" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="G100" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="H100" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A101" s="13">
-        <v>42</v>
-      </c>
-      <c r="B101" s="14" t="s">
+      <c r="B55" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="C101" s="14" t="s">
+      <c r="C55" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="D101" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E101" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="F101" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="G101" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="H101" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
+      <c r="D55" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="E55" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="F55" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="G55" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="H55" s="13" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="65" s="15" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="66" s="15" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="67" s="15" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="68" s="15" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="69" s="15" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="70" s="15" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="71" s="15" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="72" s="15" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="73" s="15" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="74" s="15" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="75" s="15" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="76" s="15" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="77" s="15" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="78" s="15" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="79" s="15" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="80" s="15" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="81" s="15" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="82" s="15" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="83" s="15" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="84" s="15" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="85" s="15" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="86" s="15" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="87" s="15" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="88" s="15" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="89" s="15" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="90" s="15" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="91" s="15" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="92" s="15" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="93" s="15" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="94" s="15" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="95" s="15" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="96" s="15" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="97" s="15" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="98" s="15" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="99" s="15" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="100" s="15" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="101" s="15" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="102" s="15" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <conditionalFormatting sqref="E1:H1048576">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
